--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/MINNESOTA_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/MINNESOTA_2023.xlsx
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C271">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C604">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C605">
